--- a/results/Int Task Remove ACC 0.5/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.5/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0006631347168333946</v>
+        <v>-0.001157210048134131</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.003779775742819665</v>
+        <v>-0.007534580976383114</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0003809680448850205</v>
+        <v>-0.00167885524158675</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0001666001780553827</v>
+        <v>0.000530435386212015</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0001752099440357913</v>
+        <v>-0.002759142535847907</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001668231451211333</v>
+        <v>-0.0007707267485900871</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.642780767639908e-05</v>
+        <v>2.720243235454723e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004062875391705567</v>
+        <v>-0.001679388447310159</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01045440200822347</v>
+        <v>0.01532547915906914</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01391375072870037</v>
+        <v>0.0162075169338332</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001303096120014791</v>
+        <v>0.0006239976197740837</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001615279420934256</v>
+        <v>-0.002896078782792457</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0009854184507172002</v>
+        <v>-0.00394926672255023</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.005696480857785402</v>
+        <v>-0.006992203112909575</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006134750441231347</v>
+        <v>0.008460881866530814</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0002510648829208218</v>
+        <v>0.001644011128645963</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001333641482625799</v>
+        <v>-0.0003730600969847985</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0005951483887230991</v>
+        <v>-0.0007378223569166908</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.001651657757247488</v>
+        <v>-0.002909903841892314</v>
       </c>
       <c r="V3" t="n">
-        <v>8.426128376492703e-05</v>
+        <v>-9.730087922790066e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00094075745084519</v>
+        <v>-0.001071094336594867</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001082557284088155</v>
+        <v>-0.0003883045593502374</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.00177295753868291</v>
+        <v>0.0006701075056390404</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0001700851192137865</v>
+        <v>0.0006125447051835741</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.0007827824085947611</v>
+        <v>-0.0003396943166647558</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0001093332849427141</v>
+        <v>-1.041928266969357e-06</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.001613928362694262</v>
+        <v>-0.000780083885841748</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.001302671686224093</v>
+        <v>-0.001224928880031161</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0004273650348484292</v>
+        <v>-0.0006189068598462578</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.002376243810676559</v>
+        <v>-0.002972975813396585</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.000154563375425496</v>
+        <v>1.855585227654943e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0004569228263794056</v>
+        <v>0.0002470042183858124</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0004802567167593963</v>
+        <v>0.001124469421075268</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.0002709141709379647</v>
+        <v>-0.001923556705129759</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4.704296125400648e-06</v>
+        <v>0.0001797338197930931</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0002570959235931636</v>
+        <v>0.0003226893299682077</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0003663844108725245</v>
+        <v>-0.0009828320888561491</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001471453715488237</v>
+        <v>-0.001535738550688157</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0001724241876847987</v>
+        <v>0.0001051362565286662</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-3.507644489645298e-06</v>
+        <v>0.0001674601823062361</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.000566077696771442</v>
+        <v>0.0007413209995760629</v>
       </c>
       <c r="AS3" t="n">
-        <v>-1.520537014984768e-05</v>
+        <v>0.000519550393730851</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0001044952027908929</v>
+        <v>0.0008029358244228589</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.002753933270102077</v>
+        <v>-0.007407318446539106</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.002209225451511033</v>
+        <v>-0.001447277662185968</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.00194462207456093</v>
+        <v>-0.003432635137315152</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0002394629661581016</v>
+        <v>-6.665272224195542e-06</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.001630657831743797</v>
+        <v>-0.004551647854734543</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.002051516703896277</v>
+        <v>-0.00267256864795145</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0002418297232976684</v>
+        <v>-0.0003835188632726036</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.0001009667575203751</v>
+        <v>0.0009734119545768572</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.000315650714257637</v>
+        <v>-0.0001715806774600581</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0004809253899145549</v>
+        <v>-0.0001052334800637977</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0007304057561797518</v>
+        <v>-0.0008855695368332215</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.003220211097958495</v>
+        <v>0.0004282144733707516</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.004067758178414074</v>
+        <v>-0.001477016306953099</v>
       </c>
       <c r="BH3" t="n">
-        <v>-5.219206680584509e-06</v>
+        <v>0.0001889763779527609</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.0002135706045056162</v>
+        <v>-0.0001320043313555819</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.002231084324462716</v>
+        <v>-0.004287393673808254</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.000985602273799838</v>
+        <v>-0.0004448602717089319</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0006245308380208469</v>
+        <v>0.0001798585789051588</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.002533376774190456</v>
+        <v>-0.001085966370138191</v>
       </c>
       <c r="BN3" t="n">
-        <v>-2.457306974003699e-05</v>
+        <v>0.001708117097130856</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.00100537330632978</v>
+        <v>-0.003605955746191843</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0008501159831029402</v>
+        <v>-0.001211765151801017</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-5.51286985978805e-05</v>
+        <v>6.883809990330559e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0003238952921713378</v>
+        <v>-0.001568447094324557</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0005830300069420236</v>
+        <v>-0.002333340644561005</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0003543273197715269</v>
+        <v>-0.0006593203760429257</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.002239210017587566</v>
+        <v>-0.002275234513113737</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0001222832338242519</v>
+        <v>-0.0012768687708788</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.0006088899821240133</v>
+        <v>-0.002845425969462171</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0001994949395346646</v>
+        <v>-2.72729090957391e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0001314941802635972</v>
+        <v>0.0001825937781731868</v>
       </c>
       <c r="BZ3" t="n">
-        <v>9.309602997324417e-05</v>
+        <v>-0.0005190795598057031</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.000120526735587485</v>
+        <v>-1.230769080052152e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.001871180453136701</v>
+        <v>-0.002979718421501717</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0001564200416429818</v>
+        <v>5.543803844651363e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0006390215335394955</v>
+        <v>-7.345450972398026e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0005061045916529338</v>
+        <v>-0.002606028933335745</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0004429084780509439</v>
+        <v>-0.001923009081061058</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.001050247269352737</v>
+        <v>-0.0003157793161359867</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0007150034351996161</v>
+        <v>-0.004217245541839324</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.0007030173495704271</v>
+        <v>-0.004360987954832741</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0001570904051578736</v>
+        <v>0.0006259964996177082</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003542535827132533</v>
+        <v>0.004826310815361907</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006105664356218299</v>
+        <v>0.01228967373858109</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003049025374718324</v>
+        <v>0.002656417764475412</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004129307105056866</v>
+        <v>0.006678532505905214</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003468562950225156</v>
+        <v>0.003972943987894028</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005933640715059146</v>
+        <v>0.006468288708210659</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003564264157176531</v>
+        <v>0.0002081458345455523</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007422695267183059</v>
+        <v>0.003300692502321356</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01090585053137018</v>
+        <v>0.01444367513339426</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01632847641990175</v>
+        <v>0.01487105595206409</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003687424076825638</v>
+        <v>0.005994970773771298</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002454837936237347</v>
+        <v>0.007489743278798859</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004191535069534109</v>
+        <v>0.008760997406604085</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02009433957404638</v>
+        <v>0.02704114730452445</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02437699399034006</v>
+        <v>0.02919301738383318</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0057000664586372</v>
+        <v>0.00454610262671121</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004079107344905029</v>
+        <v>0.004034125358989103</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006204693633886483</v>
+        <v>0.003220299543729033</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003784396013078316</v>
+        <v>0.00533075521332294</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0001838419003242691</v>
+        <v>0.0003177802613673221</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003126766835936857</v>
+        <v>0.005696423088796809</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002098807912002186</v>
+        <v>0.007672843473966996</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00421641599639626</v>
+        <v>0.004653679442235651</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002382740264709628</v>
+        <v>0.002382169239378091</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002292122567602539</v>
+        <v>0.002218825794606331</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001161957404226452</v>
+        <v>0.0006689213113180468</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004377993106832887</v>
+        <v>0.004307411451017124</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004006454915328869</v>
+        <v>0.006179009874726757</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004130842125179101</v>
+        <v>0.003994331690595571</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.006748220414850199</v>
+        <v>0.005948498845559222</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0004892729429412825</v>
+        <v>0.0003322199118106565</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001215764086704089</v>
+        <v>0.0006171669921660997</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004807010056558382</v>
+        <v>0.002857770578361405</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.003826170727698152</v>
+        <v>0.003767884267700855</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001152844620225101</v>
+        <v>0.0003844830063269125</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0007011850853291591</v>
+        <v>0.0005362315336221307</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002386361810869655</v>
+        <v>0.003533426710811614</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003097219706326347</v>
+        <v>0.006580620185001124</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001017114687341938</v>
+        <v>0.0006893543154164936</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002344961610012207</v>
+        <v>0.002867891506751576</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.003558959663180448</v>
+        <v>0.002268387497305722</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002814470011315699</v>
+        <v>0.003202325057577989</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.01205646202257348</v>
+        <v>0.008636506629102831</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.009771173167534597</v>
+        <v>0.01317309630482118</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.003732407304186947</v>
+        <v>0.005113599945163238</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.004878539432013774</v>
+        <v>0.0062674123533814</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0007374493418562232</v>
+        <v>0.0006370844301743427</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003682236583269003</v>
+        <v>0.00930790294207494</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.007235008837507609</v>
+        <v>0.005290407359881303</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.008850518773704382</v>
+        <v>0.004974118984104357</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.009089418072486135</v>
+        <v>0.004975525236019665</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001216089507220092</v>
+        <v>0.0006437648009353961</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001242167889343644</v>
+        <v>0.0008483851860389553</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001986065193422441</v>
+        <v>0.003918330702726735</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.01275938410130436</v>
+        <v>0.006506256903753453</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.009411273263251436</v>
+        <v>0.007970854533987362</v>
       </c>
       <c r="BH4" t="n">
-        <v>1.650458068981396e-05</v>
+        <v>0.000597595778299552</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.002110976114771512</v>
+        <v>0.0006734305785513318</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.008015265360357005</v>
+        <v>0.005292035703447821</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0113504720853169</v>
+        <v>0.008318597568810052</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0004953229723636452</v>
+        <v>0.001005181485868462</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.007308095612192933</v>
+        <v>0.00634401126165579</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.007417750482610686</v>
+        <v>0.006091762038510543</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.01186438594739913</v>
+        <v>0.01015488137804709</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.005344882337232305</v>
+        <v>0.003190129818922615</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0002518726277437215</v>
+        <v>0.000221376953237193</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.003628216188264582</v>
+        <v>0.005730559248288304</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003508237218856925</v>
+        <v>0.005144884818051905</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001027211580072146</v>
+        <v>0.001071422333043397</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.004201251700621685</v>
+        <v>0.006663213378620687</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001996757589636833</v>
+        <v>0.003358172025877878</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.007620754373445998</v>
+        <v>0.004985790407791043</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0004216370349440994</v>
+        <v>8.823254159011809e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0005243230739534334</v>
+        <v>0.001049298999220905</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0006426985893681497</v>
+        <v>0.001079400028236118</v>
       </c>
       <c r="CA4" t="n">
         <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.000413333642193052</v>
+        <v>0.001770242006775479</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.003120174951315273</v>
+        <v>0.006919817783582242</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.000462432691623202</v>
+        <v>0.0001240418373943183</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0009931847211623126</v>
+        <v>0.0007828935219732169</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003321399847639167</v>
+        <v>0.005487771325214912</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004005786448961899</v>
+        <v>0.005819985518055544</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.002018251612169733</v>
+        <v>0.002460813628042396</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.006286070782054168</v>
+        <v>0.006141309676318205</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.00558603139596939</v>
+        <v>0.006658943408668601</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.00216762976895101</v>
+        <v>0.002463290163863685</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.008117036337895223</v>
+        <v>-0.01294363256784969</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01587901701323247</v>
+        <v>-0.03355949895615867</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.005904404873477076</v>
+        <v>-0.008141962421711946</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.006141732283464529</v>
+        <v>-0.01196850393700785</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.005984251968503884</v>
+        <v>-0.01315240083507307</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.007034120734908111</v>
+        <v>-0.0142924086223055</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.000567107750472573</v>
+        <v>-0.0002811621368322026</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01576215195847096</v>
+        <v>-0.006106471816283943</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.002689721421709845</v>
+        <v>-0.005564304461942227</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.004934383202099712</v>
+        <v>-0.003202099737532771</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.003937007874015741</v>
+        <v>-0.007933194154488543</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.002782152230971091</v>
+        <v>-0.02379958246346557</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.008503937007873974</v>
+        <v>-0.02509186351706033</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.05490813648293959</v>
+        <v>-0.07863517060367452</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0506561679790026</v>
+        <v>-0.05685039370078737</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01035613870665422</v>
+        <v>-0.003701968134957789</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01099575271354413</v>
+        <v>-0.01044985941893156</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.009372071227741363</v>
+        <v>-0.006771653543307055</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.006837160751565719</v>
+        <v>-0.01706680584551147</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0001405810684161457</v>
+        <v>-0.0006299212598425141</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.003097112860892348</v>
+        <v>-0.01207349081364827</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.001815766164747501</v>
+        <v>-0.01664926931106472</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.01298031865042181</v>
+        <v>-0.003467666354264254</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.005154639175257792</v>
+        <v>-0.002249297094657887</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.006023029229406507</v>
+        <v>-0.004069767441860472</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.002024850437183634</v>
+        <v>-0.001154855643044572</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.008966493629070316</v>
+        <v>-0.006229353468617327</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.006002087682672197</v>
+        <v>-0.01443298969072162</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.00535872453498667</v>
+        <v>-0.008924843423799612</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01790065604498599</v>
+        <v>-0.01089459698848536</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0007874015748030927</v>
+        <v>-0.0005249343832020803</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.002689948088721095</v>
+        <v>-0.0009840674789127978</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01007497656982198</v>
+        <v>-0.002761159687068615</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.009133611691022957</v>
+        <v>-0.009787422497785626</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002624179943767613</v>
+        <v>-0.0003362151777137168</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.000849457291175093</v>
+        <v>-0.0006129184347005712</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.004295837023914917</v>
+        <v>-0.008724534986713894</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.001008645533141184</v>
+        <v>-0.01691022964509393</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.002024850437183623</v>
+        <v>-0.001096033402922747</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.003631532329495079</v>
+        <v>-0.003779527559055096</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.005233380480905226</v>
+        <v>-0.002268431001890314</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.006419868791002881</v>
+        <v>-0.007591377694470447</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01911623439000957</v>
+        <v>-0.01008645533141208</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.02387068201948623</v>
+        <v>-0.03148804251550043</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.01115276476101223</v>
+        <v>-0.01227741330834111</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01368322399250239</v>
+        <v>-0.01508903467666353</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001409185803757818</v>
+        <v>-0.000895803866100875</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.009137769447047861</v>
+        <v>-0.02959290187891439</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.01602624179943773</v>
+        <v>-0.0103188662533215</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01460134486071079</v>
+        <v>-0.008247422680412352</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01049671977507034</v>
+        <v>-0.007449316360207403</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001594331266607563</v>
+        <v>-0.001096033402922747</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0008434864104967632</v>
+        <v>-0.001878914405010423</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.006067316209034501</v>
+        <v>-0.01129317980513728</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.03381364073006719</v>
+        <v>-0.01087160262417991</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02169634489222123</v>
+        <v>-0.01448796602170838</v>
       </c>
       <c r="BH5" t="n">
-        <v>-5.219206680584509e-05</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.005857544517338387</v>
+        <v>-0.001171508903467633</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.02347703842549209</v>
+        <v>-0.01435281837160751</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01109013685700802</v>
+        <v>-0.01160318866253319</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0001840773124712314</v>
+        <v>-0.00196813495782564</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.02155576382380512</v>
+        <v>-0.01804123711340203</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01485473289597005</v>
+        <v>-0.007012487992315053</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.0218777679362267</v>
+        <v>-0.02564216120460581</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.01019348749410098</v>
+        <v>-0.00604058518168954</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0007550731477111938</v>
+        <v>-0.000157480314960623</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.006742102781706727</v>
+        <v>-0.01346555323590815</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.004514889529298694</v>
+        <v>-0.01471816283924843</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001288541187298664</v>
+        <v>-0.00292294065544727</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.01151486550259554</v>
+        <v>-0.01591858037578286</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.003410097431355141</v>
+        <v>-0.007449316360207392</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.01845210004719207</v>
+        <v>-0.01163883089770357</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0009394572025052117</v>
+        <v>-0.0001771479185119329</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.000849457291175093</v>
+        <v>-0.0009840674789127978</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.0006784968684759862</v>
+        <v>-0.002348643006263029</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.0008506616257088595</v>
+        <v>-0.003496868475991621</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.007739499764039625</v>
+        <v>-0.02004175365344468</v>
       </c>
       <c r="CD5" t="n">
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0023622047244094</v>
+        <v>-0.001200417536534437</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.003583215464403544</v>
+        <v>-0.01544885177453026</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.005447298494242647</v>
+        <v>-0.01153444676409188</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0008283479061205412</v>
+        <v>-0.007202505219206723</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.006111603188662473</v>
+        <v>-0.01941544885177455</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.009344030202925901</v>
+        <v>-0.018580375782881</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.0053235908141962</v>
+        <v>-0.00327723649247118</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002018924656731244</v>
+        <v>-0.001417367931336855</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.007843080896165941</v>
+        <v>-0.007034654128152109</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002338775556513617</v>
+        <v>-0.002423789913818725</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.003615940971872394</v>
+        <v>-0.000648423738079304</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.00126585494354573</v>
+        <v>-0.003610324997916426</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.005005964422654705</v>
+        <v>-0.001546588684148145</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0001856958400218322</v>
+        <v>-3.937007874015852e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0006345354206496651</v>
+        <v>-0.004063534649013639</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004667374715454642</v>
+        <v>0.004520396003953675</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004911426867070212</v>
+        <v>0.004909112805690563</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.003513348631698207</v>
+        <v>-0.00432801060787513</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0001626783188187153</v>
+        <v>-0.001881402117156938</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.003448598213827597</v>
+        <v>-0.003189718748352416</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.006134989893275072</v>
+        <v>-0.005841438346532474</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001341772077071851</v>
+        <v>-0.0002868667196289614</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.000621529320490688</v>
+        <v>-0.001407527756606983</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002709773174616423</v>
+        <v>-0.001113313806071242</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.002578131728369354</v>
+        <v>-0.001927738624287276</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.003920517794420511</v>
+        <v>-0.003279754551002456</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.53606789250227e-05</v>
+        <v>-0.0001769702689948111</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.002052680106158303</v>
+        <v>-0.002044804465534511</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0006570085505418876</v>
+        <v>-0.001809110576207698</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.001400968900790564</v>
+        <v>-0.001692508014595059</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0009960667133054185</v>
+        <v>-0.0006053018837658241</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0005051451036376858</v>
+        <v>-0.001613528431707004</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0008100318357908643</v>
+        <v>-0.0003368687159413547</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.004176643097175142</v>
+        <v>-0.003766923084060936</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0004108925046902801</v>
+        <v>-0.004152433711965542</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.002881927934405656</v>
+        <v>-0.002194291977896012</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.002601907078016552</v>
+        <v>-0.008895961251533593</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0005984646875482613</v>
+        <v>-0.0001676722485987714</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.001135177453027131</v>
+        <v>-6.902899217671178e-05</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.001567286141495289</v>
+        <v>-0.0009429736879168704</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.001602208429733576</v>
+        <v>-0.002116426942794217</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0002996892700697806</v>
+        <v>-3.937007874015852e-05</v>
       </c>
       <c r="AM6" t="n">
-        <v>-2.385584689556241e-05</v>
+        <v>9.325379837826221e-05</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001332475112633155</v>
+        <v>-0.002846497625887456</v>
       </c>
       <c r="AO6" t="n">
-        <v>-9.380266071011556e-05</v>
+        <v>-0.004456844961295397</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0001682549926829008</v>
+        <v>-0.0003579165629308129</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0008578816261828326</v>
+        <v>-0.00170533560083104</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.001772576432137221</v>
+        <v>-0.0009794862925021463</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0003635775715355228</v>
+        <v>0.0001740810391084702</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.005792270557197939</v>
+        <v>-0.004547479120042682</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.00470243329638333</v>
+        <v>-0.005636136389919329</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.003544409764567236</v>
+        <v>-0.004291040915592912</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.003887504359346569</v>
+        <v>-0.006261705982062182</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0005672480162867588</v>
+        <v>-0.0005793710733662748</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.003973943129120042</v>
+        <v>-0.003595490539784388</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.005275835825115909</v>
+        <v>-0.005978679213178126</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.006145492446551508</v>
+        <v>-0.004296971356031101</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.00606776513409911</v>
+        <v>-0.002250116779787759</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.000258019174524235</v>
+        <v>-0.0007070252114583704</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0002252874331302446</v>
+        <v>-9.431864687840519e-05</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0009683478687391113</v>
+        <v>-0.0008028939897787191</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.007134240670016942</v>
+        <v>-0.000514784907885582</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.009746116428919462</v>
+        <v>-0.00451626539979062</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0.000583348032110062</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.003327795592660865</v>
+        <v>-0.004347377079475728</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.005804136578222741</v>
+        <v>-0.004038776944704778</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0003879380088480128</v>
+        <v>-0.0002363888797517366</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.002757317949535251</v>
+        <v>-0.0007546396686657159</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.00308939971360232</v>
+        <v>-0.001163605986812738</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.004138208344534383</v>
+        <v>-0.006000530063301368</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.002594220780301418</v>
+        <v>-0.002068939397027378</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-8.326672684688675e-18</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001257752532863876</v>
+        <v>-0.00396596372269657</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.00298731460606563</v>
+        <v>-0.002322091813994925</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.000359902294312589</v>
+        <v>-0.00111645148093108</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.003555202171317715</v>
+        <v>-0.003238340307469376</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001256176353622418</v>
+        <v>-0.003671578894996158</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.001190117170774504</v>
+        <v>-0.004477510733485052</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0004105851404262756</v>
+        <v>-5.108516777483363e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0002124147679059773</v>
+        <v>-0.0003779325745158629</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0005322841892807434</v>
+        <v>-0.001375818287286173</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0003885366445333632</v>
+        <v>-0.0003340606428645615</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.003371952557283367</v>
+        <v>-0.004394772130009356</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.00151945644640607</v>
+        <v>-0.0006129963094064106</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001970622824775034</v>
+        <v>-0.004625786584549416</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.003085003622313407</v>
+        <v>-0.004347820407624161</v>
       </c>
       <c r="CH6" t="n">
-        <v>9.794552391353961e-05</v>
+        <v>-5.964961294304127e-05</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.002685661018251257</v>
+        <v>-0.005929788537502318</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.003662139277978752</v>
+        <v>-0.004930800729116738</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0007068859291995272</v>
+        <v>-0.0001296446977671367</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0009535924922597139</v>
+        <v>-0.0002747250273914535</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001556537370180061</v>
+        <v>-0.001830507034420231</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0008450544535662851</v>
+        <v>-0.0005431102697620038</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0003451449608835422</v>
+        <v>0.0004093914211410643</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005118538282071039</v>
+        <v>-0.001487620779141979</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001641282979246538</v>
+        <v>0.0008383431514778661</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.300966405890392e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001560695058956829</v>
+        <v>-0.002794363061546501</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006867817528117293</v>
+        <v>0.01326449379710585</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006603686054575958</v>
+        <v>0.0164025946772466</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0003417484317749353</v>
+        <v>0.001168272973476786</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001570888940021442</v>
+        <v>-0.0008970508077516203</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0005470867803379131</v>
+        <v>-0.00158309754714086</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.001416878117733411</v>
+        <v>0.001820751883451949</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01163306330796516</v>
+        <v>0.008231167281765605</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001635079045351872</v>
+        <v>-8.643209358150106e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.001165271940944557</v>
+        <v>0.0003857119719411162</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0004642287812182788</v>
+        <v>-0.0008329735602355003</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.002051139542148916</v>
+        <v>-0.001442917113202808</v>
       </c>
       <c r="V7" t="n">
-        <v>4.910569746182647e-05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001716518579982074</v>
+        <v>-0.0006616257088846778</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001061283872841423</v>
+        <v>-1.83802673080492e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.0009799115909204848</v>
+        <v>0.0001606200687660764</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0006911467186241415</v>
+        <v>7.469561283013901e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>-9.713518796916065e-05</v>
+        <v>-0.0002014723407098462</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001665640679222091</v>
+        <v>-0.0001107174490699525</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.001369980861079972</v>
+        <v>-0.00126028906122081</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001578534118350294</v>
+        <v>9.065527564354192e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001328475341369384</v>
+        <v>0.0004947709866855388</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.000958481813081935</v>
+        <v>-0.0005043227665705973</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0001635862055141102</v>
+        <v>-2.343017806933911e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>9.606147934681509e-05</v>
+        <v>0.0002720563822104616</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0004074895267565437</v>
+        <v>0.0008357662809646005</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0001614179267628469</v>
+        <v>-0.0003339391248094736</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0003433976693507645</v>
+        <v>4.844961240310086e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>7.350569836618303e-05</v>
+        <v>0.0001751722412096146</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.0003070233392414079</v>
+        <v>-0.0001405810684160902</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0003964634727423477</v>
+        <v>0.001403832645253755</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0001258877293803806</v>
+        <v>0.0001144284947504126</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0001204627294171867</v>
+        <v>-0.0004484660549415654</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.0009390009265771771</v>
+        <v>0.0007842460286523967</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0007072692821537274</v>
+        <v>0.001033854423648361</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.001339157894384308</v>
+        <v>0.001745661445858188</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0002703336434531078</v>
+        <v>-0.003154764499466001</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.001582091321844248</v>
+        <v>0.0002943431008465225</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0006501636459326887</v>
+        <v>-0.001142349351945221</v>
       </c>
       <c r="AX7" t="n">
-        <v>-9.653725336817854e-05</v>
+        <v>0.0001404882686387166</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0002524943866880791</v>
+        <v>-0.001457646645913419</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.0008497985581739751</v>
+        <v>-0.00268706280437368</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0021959828307973</v>
+        <v>4.753749747108961e-05</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.001632358686772578</v>
+        <v>0.00112064915033343</v>
       </c>
       <c r="BC7" t="n">
-        <v>-2.617229557072555e-06</v>
+        <v>-0.0001534364890435125</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0002034540411010866</v>
+        <v>-2.357378595000959e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>-2.624671916010013e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0001403077435391921</v>
+        <v>0.001170406497660098</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0009900468093120506</v>
+        <v>-0.001373632486931753</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0001185333282488099</v>
+        <v>-0.0002150466728213174</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0002403768348141322</v>
+        <v>-0.002974877014284277</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0006414499841937149</v>
+        <v>-0.002376564282077875</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0005506603401204068</v>
+        <v>0.0003560372078432184</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0009633756155119966</v>
+        <v>0.0004826111967473179</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0004004201392324158</v>
+        <v>0.001347778306014341</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.001315102034740895</v>
+        <v>-0.001682481679393066</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0008407165638645187</v>
+        <v>-0.001532514790232531</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0001685264615866044</v>
+        <v>-0.0006882160734653976</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.001355306177153687</v>
+        <v>-0.001190407662028647</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0004298025624652646</v>
+        <v>-0.0007211972923017174</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.002226013660918874</v>
+        <v>-0.001242545450523214</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.0005367907601943611</v>
+        <v>-0.0005352199474166929</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0002025955285353431</v>
+        <v>-0.002982662746469733</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0001894734553735566</v>
+        <v>2.506255166097592e-05</v>
       </c>
       <c r="BZ7" t="n">
-        <v>7.246498223981157e-05</v>
+        <v>-0.0002174630801902499</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-9.505577356898608e-05</v>
+        <v>-4.636829601553094e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.001638566792983687</v>
+        <v>-0.002747859428635657</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>4.515315387290109e-05</v>
+        <v>-0.0001349422552715141</v>
       </c>
       <c r="CF7" t="n">
-        <v>4.283593079897896e-05</v>
+        <v>-0.001606470755635159</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0005146692893936099</v>
+        <v>-0.002039147913538869</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0005280190659489314</v>
+        <v>0.0003085654555625983</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.0004691779929097528</v>
+        <v>-0.002270899998929809</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.001080210995969927</v>
+        <v>-0.001350483089180748</v>
       </c>
       <c r="CK7" t="n">
-        <v>6.509097667443671e-05</v>
+        <v>0.0002493810438156663</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001241537858433306</v>
+        <v>0.0009470630187073531</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0002776245273735461</v>
+        <v>-0.0007448605852064666</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001692177050478108</v>
+        <v>-0.0001060820367750681</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003025188316173791</v>
+        <v>0.003931032451461041</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001341963507807761</v>
+        <v>-0.0007146834827731429</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003501107730382452</v>
+        <v>0.002877821561379545</v>
       </c>
       <c r="I8" t="n">
-        <v>3.32152347210124e-05</v>
+        <v>9.62704544706261e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004587252733104438</v>
+        <v>0.0005556685617374407</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01629433275018988</v>
+        <v>0.02855256166352755</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01901196910844517</v>
+        <v>0.02035033079703923</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003542613097834077</v>
+        <v>0.003660414929389716</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003514997222098018</v>
+        <v>0.0002084877182276012</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001542758233037164</v>
+        <v>0.0003664500289637523</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003588608139810135</v>
+        <v>0.005969088338107456</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01370938241020212</v>
+        <v>0.01545983166178337</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001661651242965623</v>
+        <v>0.004224056712514896</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001383039196646757</v>
+        <v>0.001539231422926704</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0001328609388840107</v>
+        <v>0.0003770564219629708</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0007235433827256304</v>
+        <v>-2.357378594999293e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001807428910082648</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003506104371914245</v>
+        <v>0.000411402832696639</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002349347093233234</v>
+        <v>0.002654702653365029</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0006100766494337607</v>
+        <v>0.0006466160808775795</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009347285607936295</v>
+        <v>0.0005819248832571511</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.000218729914580823</v>
+        <v>0.0007460653835468178</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0004693709242498651</v>
+        <v>0.0005854506021623435</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0006390198681560516</v>
+        <v>0.0006132768411094031</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002003830655778546</v>
+        <v>0.00329704061680928</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.003417719263620644</v>
+        <v>0.00173381831997341</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002181550014304723</v>
+        <v>0.001167487292882735</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.000275790872888379</v>
+        <v>0.0002888749612046354</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.000225253007028306</v>
+        <v>0.000589109588276035</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.003111388560208325</v>
+        <v>0.002093048435686975</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.002255530341898934</v>
+        <v>7.828810020876208e-05</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0005214026938604843</v>
+        <v>0.000271438046801345</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0004649493858328885</v>
+        <v>0.0006012061583039712</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0007358427943599865</v>
+        <v>0.0008196412221734284</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.002076307412781983</v>
+        <v>0.003178028970853247</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0008628380346652337</v>
+        <v>0.0005971656911970242</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0009942761231034796</v>
+        <v>0.001240247120525362</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0007381235618702991</v>
+        <v>0.002139534989782971</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001983226306465869</v>
+        <v>0.002152355450667187</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.004603901660435908</v>
+        <v>0.003536695271155951</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.003009096740178685</v>
+        <v>-0.0005997980439764544</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0003858957718763739</v>
+        <v>0.0008804430229501309</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0007351931632289588</v>
+        <v>0.0006372450461318679</v>
       </c>
       <c r="AX8" t="n">
-        <v>-1.181474480149436e-05</v>
+        <v>0.0003309492757161026</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0004152141873355192</v>
+        <v>-0.0003101683926251125</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.003271053190165973</v>
+        <v>-0.0004744053101323365</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.008030913171423446</v>
+        <v>0.00220110736237899</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.002881447570351533</v>
+        <v>0.00512109451624855</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.001067678251955212</v>
+        <v>0.0003233297051443818</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0006858250301822244</v>
+        <v>0.0003783460784981208</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.243644688475382e-05</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.004909364472163136</v>
+        <v>0.005203937149221155</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.003089025209058197</v>
+        <v>0.003495288388874429</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0007111197000098906</v>
+        <v>0.0002755905511811097</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002177578905698188</v>
+        <v>-0.0005117190498119484</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.004055823295379637</v>
+        <v>0.002616623490704814</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0009865370902417182</v>
+        <v>0.0008256415103644553</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001252502208092845</v>
+        <v>0.001376370555455117</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.00292281738530076</v>
+        <v>0.005737647556972122</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001309313952578969</v>
+        <v>0.003946978683047439</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0005507233787470172</v>
+        <v>0.0005298937923457342</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.451449608835589e-05</v>
+        <v>8.082701010969917e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001769205116558234</v>
+        <v>0.0003495734434499575</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.000947895684551081</v>
+        <v>-0.0003318262394586435</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001231934123836473</v>
+        <v>-4.26355445025478e-05</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0.0001998641884880442</v>
+        <v>-0.0006950779223633769</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001028946692494556</v>
+        <v>0.001226044026596063</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001563302839398661</v>
+        <v>-2.991520872568933e-05</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0003683406969417491</v>
+        <v>0.0003430373429073958</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0005894670232883314</v>
+        <v>0.0003198910845386566</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0001847189159494611</v>
+        <v>0.0001414427157001574</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0007443289224953021</v>
+        <v>0.00089386917092735</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>8.386085431161261e-05</v>
+        <v>0.0002596144728612415</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002673889337869767</v>
+        <v>-3.633720930235896e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0007944123905270245</v>
+        <v>-7.236026405736397e-05</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001364631691488241</v>
+        <v>0.000837812273474664</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001383917022134296</v>
+        <v>-0.001561888080724039</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.001437208752802535</v>
+        <v>-0.0006812934106743551</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0012185672737593</v>
+        <v>0.001331526595625859</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00509193776520509</v>
+        <v>0.005668733392382675</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003197674418604568</v>
+        <v>0.002162908421537013</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004341670599339331</v>
+        <v>0.001017441860465107</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006889352818371652</v>
+        <v>0.009864300626304789</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005851816894761708</v>
+        <v>0.001008645533141217</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01164545025931167</v>
+        <v>0.007590759075907639</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007684918347743208</v>
+        <v>0.0004253308128544964</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008611691022964552</v>
+        <v>0.004187758858720625</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03294573643410847</v>
+        <v>0.03585271317829453</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04345930232558136</v>
+        <v>0.04229651162790694</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005377906976744085</v>
+        <v>0.01134215500945185</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004650132860938949</v>
+        <v>0.001732283464566975</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004479019330504486</v>
+        <v>0.005810684161199675</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0173934108527131</v>
+        <v>0.01429919773478051</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.04530038759689919</v>
+        <v>0.05154639175257734</v>
       </c>
       <c r="R9" t="n">
-        <v>0.008768267223382087</v>
+        <v>0.008872651356993722</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003808680248007157</v>
+        <v>0.004074402125775057</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01440501043841337</v>
+        <v>0.005636743215031293</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004417855499309698</v>
+        <v>0.001380579843534257</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0004803073967339921</v>
+        <v>0.0004686035613870931</v>
       </c>
       <c r="W9" t="n">
-        <v>0.005014058106841579</v>
+        <v>0.01076173604960145</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004264292408622227</v>
+        <v>0.01333038086802482</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001748734468476742</v>
+        <v>0.01307086614173232</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002925908447380876</v>
+        <v>0.0053235908141962</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00172910662824215</v>
+        <v>0.003810020876826692</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001885902876001921</v>
+        <v>0.000849457291175082</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.006724303554274802</v>
+        <v>0.008402922755741093</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.009399224806201456</v>
+        <v>0.006134969325153339</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.006948918545789218</v>
+        <v>0.004530438886267052</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.00414698162729662</v>
+        <v>0.005669291338582705</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0005219206680584509</v>
+        <v>0.0005314437555358875</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0008434864104966744</v>
+        <v>0.001328609388839697</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.007461240310077421</v>
+        <v>0.005688935281837138</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.004243281471004256</v>
+        <v>0.001969260326609057</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001368570080226539</v>
+        <v>0.0008350730688935215</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.001827553889409506</v>
+        <v>0.001328609388839708</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.004018789144050116</v>
+        <v>0.003680981595091959</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.009593023255813859</v>
+        <v>0.003517060367454072</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001536983669548575</v>
+        <v>0.001151461470327753</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.003914405010438405</v>
+        <v>0.006155890168290545</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0073630924988495</v>
+        <v>0.005060918462980357</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.00250117980179333</v>
+        <v>0.004118689105403028</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.02671916010498691</v>
+        <v>0.01952755905511815</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.00901162790697665</v>
+        <v>0.006663516068052977</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.001488952929875176</v>
+        <v>0.006666666666666732</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003884514435695552</v>
+        <v>0.004801670146137749</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001242521859180812</v>
+        <v>0.001200768491834803</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.002180232558139461</v>
+        <v>0.002457466918714612</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.006459217350306479</v>
+        <v>0.008451443569553841</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.009081364829396366</v>
+        <v>0.007307351638618276</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.02165697674418597</v>
+        <v>0.007372400756143704</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.002713987473903945</v>
+        <v>0.0006600660066007236</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.00368098159509207</v>
+        <v>0.0009203865623561569</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0009664058904739648</v>
+        <v>0.003795688847235268</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.009980620155038667</v>
+        <v>0.007550731477111827</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.005812854442344073</v>
+        <v>0.01115311909262763</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>0.001889763779527609</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.002029259084473834</v>
+        <v>0.0009743135518157752</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00414698162729662</v>
+        <v>0.000624399615754101</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.02918635170603679</v>
+        <v>0.01916010498687668</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001296829971181623</v>
+        <v>0.00128854118729862</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.005184108527131681</v>
+        <v>0.005225863596102776</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.01303294573643402</v>
+        <v>0.01249343832020999</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.02281976744186039</v>
+        <v>0.007073643410852615</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01118110236220476</v>
+        <v>0.004540709812108534</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0001565762004175353</v>
+        <v>0.0006643046944198483</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.007183364839319517</v>
+        <v>0.009186351706036777</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.007024988213107042</v>
+        <v>0.003869749882019757</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001617954070981198</v>
+        <v>0.0007751937984496138</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.003842459173871327</v>
+        <v>0.01097112860892393</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003674540682414718</v>
+        <v>0.002929875120076908</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.00916824196597359</v>
+        <v>0.005482041587901753</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0004871567759079376</v>
+        <v>0.0001453488372093026</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0009840674789127867</v>
+        <v>0.002878653675819354</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0009743135518158419</v>
+        <v>0.0008903467666354526</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0004428697962799322</v>
+        <v>0.003832020997375352</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.002108716026241764</v>
+        <v>0.005354330708661448</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.001469816272965918</v>
+        <v>0.0003653444676409157</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0002422480620155043</v>
+        <v>0.001392891450528366</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.006292026897214286</v>
+        <v>0.004461942257217888</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.007926509186351738</v>
+        <v>0.01112860892388455</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.006367432150313201</v>
+        <v>0.001049868766404238</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01706036745406828</v>
+        <v>0.003402646502835582</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.009921259842519726</v>
+        <v>0.001370510396975477</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.002545968882602567</v>
+        <v>0.004958246346555295</v>
       </c>
     </row>
   </sheetData>
